--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104696_W27.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104696_W27.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8274</v>
+        <v>6.0175</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4276</v>
+        <v>4.371</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3998</v>
+        <v>1.6465</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4251</v>
+        <v>2.4119</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9885</v>
+        <v>0.9853</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4366</v>
+        <v>1.4266</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4613</v>
+        <v>2.4244</v>
       </c>
       <c r="K2" t="n">
-        <v>1.9497</v>
+        <v>1.9338</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5116000000000001</v>
+        <v>0.4906</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0362</v>
+        <v>-0.0125</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9485</v>
       </c>
       <c r="O2" t="n">
-        <v>0.925</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2338</v>
+        <v>0.4542</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3176</v>
+        <v>0.3202</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0838</v>
+        <v>0.1339</v>
       </c>
       <c r="V2" t="n">
-        <v>4.7563</v>
+        <v>4.7449</v>
       </c>
       <c r="W2" t="n">
-        <v>4.3707</v>
+        <v>4.3579</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5634</v>
+        <v>4.8904</v>
       </c>
       <c r="E3" t="n">
-        <v>1.903</v>
+        <v>2.3178</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6604</v>
+        <v>2.5726</v>
       </c>
       <c r="G3" t="n">
-        <v>3.1287</v>
+        <v>3.1314</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2627</v>
+        <v>1.2555</v>
       </c>
       <c r="I3" t="n">
-        <v>1.866</v>
+        <v>1.8759</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5357</v>
+        <v>2.5122</v>
       </c>
       <c r="K3" t="n">
-        <v>1.7521</v>
+        <v>1.7302</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7837</v>
+        <v>0.782</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5929</v>
+        <v>0.6192</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4894</v>
+        <v>-0.4747</v>
       </c>
       <c r="O3" t="n">
-        <v>1.0823</v>
+        <v>1.0939</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4367</v>
+        <v>0.7575</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0212</v>
+        <v>0.4689</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4155</v>
+        <v>0.2886</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X3" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. KRAMPELJ</t>
+          <t>A. FONT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9333</v>
+        <v>1.5235</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6942</v>
+        <v>0.0682</v>
       </c>
       <c r="F4" t="n">
-        <v>0.239</v>
+        <v>1.4553</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.5654</v>
+        <v>1.8695</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0072</v>
+        <v>0.669</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.5726</v>
+        <v>1.2006</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1963</v>
+        <v>1.5665</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9453</v>
+        <v>0.5688</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.749</v>
+        <v>0.9977</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7617</v>
+        <v>0.303</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0619</v>
+        <v>0.1002</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8236</v>
+        <v>0.2028</v>
       </c>
       <c r="P4" t="n">
-        <v>1.361</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R4" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4591</v>
+        <v>0.1092</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0484</v>
+        <v>-0.1326</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5075</v>
+        <v>0.2418</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3214</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8678</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. PETRASEK</t>
+          <t>M. KRAMPELJ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9094</v>
+        <v>1.1942</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0217</v>
+        <v>1.1743</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9312</v>
+        <v>0.0199</v>
       </c>
       <c r="G5" t="n">
-        <v>4.1184</v>
+        <v>-0.5599</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1384</v>
+        <v>1.0053</v>
       </c>
       <c r="I5" t="n">
-        <v>2.98</v>
+        <v>-1.5653</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4987</v>
+        <v>0.1816</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9741</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>1.5246</v>
+        <v>-0.7524</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6197</v>
+        <v>-0.7416</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8357</v>
+        <v>0.0713</v>
       </c>
       <c r="O5" t="n">
-        <v>1.4555</v>
+        <v>-0.8129</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.722</v>
+        <v>1.3658</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.8562</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="S5" t="n">
-        <v>1.152</v>
+        <v>0.7039</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3357</v>
+        <v>0.448</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8163</v>
+        <v>0.2559</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.639</v>
+        <v>-0.3155</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.639</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. FONT</t>
+          <t>L. PETRASEK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8487</v>
+        <v>1.0548</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3412</v>
+        <v>0.3704</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1898</v>
+        <v>0.6844</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8673</v>
+        <v>4.1232</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6651</v>
+        <v>1.1456</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2021</v>
+        <v>2.9776</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5763</v>
+        <v>3.4764</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5715</v>
+        <v>1.965</v>
       </c>
       <c r="L6" t="n">
-        <v>1.0048</v>
+        <v>1.5114</v>
       </c>
       <c r="M6" t="n">
-        <v>0.291</v>
+        <v>0.6468</v>
       </c>
       <c r="N6" t="n">
-        <v>0.09370000000000001</v>
+        <v>-0.8194</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1973</v>
+        <v>1.4663</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4537</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.361</v>
+        <v>-3.8697</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5649999999999999</v>
+        <v>1.2974</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5565</v>
+        <v>0.7638</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.5336</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="7">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5716</v>
+        <v>0.0898</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3901</v>
+        <v>-2.0624</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9618</v>
+        <v>2.1522</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8218</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4097</v>
+        <v>-0.4188</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2315</v>
+        <v>1.2288</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5461</v>
+        <v>0.5038</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5652</v>
+        <v>-0.5903</v>
       </c>
       <c r="L7" t="n">
-        <v>1.1114</v>
+        <v>1.0941</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2757</v>
+        <v>0.3062</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1556</v>
+        <v>0.1715</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1201</v>
+        <v>0.1347</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.1757</v>
+        <v>-3.1868</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.7635</v>
+        <v>-4.7803</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S7" t="n">
-        <v>2.2184</v>
+        <v>1.7641</v>
       </c>
       <c r="T7" t="n">
-        <v>2.1202</v>
+        <v>1.5115</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0983</v>
+        <v>0.2526</v>
       </c>
       <c r="V7" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. LAZAREVIC</t>
+          <t>A. SYLLA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.04</v>
+        <v>-0.1273</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2895</v>
+        <v>0.3543</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2495</v>
+        <v>-0.4816</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.5024</v>
+        <v>-1.4302</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.6117</v>
+        <v>-0.8241000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1094</v>
+        <v>-0.6061</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.4798</v>
+        <v>-0.4421</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.6664</v>
+        <v>-0.4794</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1866</v>
+        <v>0.0372</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0225</v>
+        <v>-0.9881</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9453</v>
+        <v>-0.3447</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0772</v>
+        <v>-0.6433</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1342</v>
+        <v>0.2276</v>
       </c>
       <c r="S8" t="n">
-        <v>3.6351</v>
+        <v>1.3029</v>
       </c>
       <c r="T8" t="n">
-        <v>2.9035</v>
+        <v>1.0241</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7316</v>
+        <v>0.2788</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. SYLLA</t>
+          <t>S. LAZAREVIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6129</v>
+        <v>-0.908</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0012</v>
+        <v>-0.4043</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6142</v>
+        <v>-0.5037</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4314</v>
+        <v>-2.4954</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.821</v>
+        <v>-2.6135</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6104000000000001</v>
+        <v>0.1181</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4373</v>
+        <v>-1.4933</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.4747</v>
+        <v>-1.6795</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0373</v>
+        <v>0.1862</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.994</v>
+        <v>-1.0022</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3463</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2268</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2268</v>
+        <v>1.1382</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8184</v>
+        <v>2.6769</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6654</v>
+        <v>2.2271</v>
       </c>
       <c r="U9" t="n">
-        <v>0.153</v>
+        <v>0.4498</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.152</v>
+        <v>-1.2463</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4956</v>
+        <v>-1.3908</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3436</v>
+        <v>0.1445</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.021</v>
+        <v>-0.0129</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6506999999999999</v>
+        <v>0.6573</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6717</v>
+        <v>-0.6703</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.123</v>
+        <v>-0.1291</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5888</v>
+        <v>0.5861</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1019</v>
+        <v>0.1162</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0619</v>
+        <v>0.0713</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.131</v>
+        <v>-0.2334</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3992</v>
+        <v>-0.2812</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2683</v>
+        <v>0.0479</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.912</v>
+        <v>-4.9071</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.5954</v>
+        <v>-4.9149</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3167</v>
+        <v>0.0078</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.3248</v>
+        <v>-3.3384</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.4313</v>
+        <v>-3.4348</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1065</v>
+        <v>0.0964</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.2968</v>
+        <v>-3.3419</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.9101</v>
+        <v>-2.9312</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.3867</v>
+        <v>-0.4107</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.028</v>
+        <v>0.0035</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5212</v>
+        <v>-0.5036</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4932</v>
+        <v>0.5071</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R11" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.039</v>
+        <v>0.9745</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1966</v>
+        <v>0.931</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2356</v>
+        <v>0.0435</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.5783</v>
+        <v>-10.098</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.7301</v>
+        <v>-8.411099999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8482</v>
+        <v>-1.6869</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.2232</v>
+        <v>-4.2265</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.1571</v>
+        <v>-3.1646</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.0662</v>
+        <v>-1.0619</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.4748</v>
+        <v>-4.5022</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.014</v>
+        <v>-3.0347</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.4608</v>
+        <v>-1.4676</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2515</v>
+        <v>0.2757</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1431</v>
+        <v>-0.13</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3946</v>
+        <v>0.4057</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R12" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4162</v>
+        <v>-0.0975</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5989</v>
+        <v>-0.0375</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1827</v>
+        <v>-0.06</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.5029</v>
+        <v>-3.4976</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.5614</v>
+        <v>-2.516500000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.258599999999999</v>
+        <v>-8.5275</v>
       </c>
       <c r="F13" t="n">
-        <v>5.697</v>
+        <v>6.010999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>0.293099999999999</v>
+        <v>0.2826999999999993</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.7182</v>
+        <v>-4.7378</v>
       </c>
       <c r="I13" t="n">
-        <v>5.0112</v>
+        <v>5.0204</v>
       </c>
       <c r="J13" t="n">
-        <v>1.0027</v>
+        <v>0.7563000000000004</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.8489</v>
+        <v>-0.9971999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>1.8518</v>
+        <v>1.7533</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.7097</v>
+        <v>-0.4738000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.8691</v>
+        <v>-3.7406</v>
       </c>
       <c r="O13" t="n">
-        <v>3.1595</v>
+        <v>3.2671</v>
       </c>
       <c r="P13" t="n">
-        <v>-10.2076</v>
+        <v>-10.2435</v>
       </c>
       <c r="Q13" t="n">
-        <v>-22.6834</v>
+        <v>-22.7632</v>
       </c>
       <c r="R13" t="n">
-        <v>12.4758</v>
+        <v>12.5198</v>
       </c>
       <c r="S13" t="n">
-        <v>8.6347</v>
+        <v>9.7097</v>
       </c>
       <c r="T13" t="n">
-        <v>6.155000000000001</v>
+        <v>7.243300000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>2.4799</v>
+        <v>2.4664</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.281799999999999</v>
+        <v>-2.265199999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>6.267</v>
+        <v>6.236199999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.5489</v>
+        <v>-8.5015</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.1149</v>
+        <v>5.3302</v>
       </c>
       <c r="E14" t="n">
-        <v>6.3747</v>
+        <v>5.0463</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2598</v>
+        <v>0.2839</v>
       </c>
       <c r="G14" t="n">
-        <v>2.4388</v>
+        <v>2.4531</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5987</v>
+        <v>2.6046</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1599</v>
+        <v>-0.1516</v>
       </c>
       <c r="J14" t="n">
-        <v>3.4399</v>
+        <v>3.4219</v>
       </c>
       <c r="K14" t="n">
-        <v>2.2858</v>
+        <v>2.2753</v>
       </c>
       <c r="L14" t="n">
-        <v>1.1541</v>
+        <v>1.1467</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.0011</v>
+        <v>-0.9689</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3129</v>
+        <v>0.3294</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.314</v>
+        <v>-1.2982</v>
       </c>
       <c r="P14" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R14" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2559</v>
+        <v>-1.0546</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1765</v>
+        <v>-0.1189</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.4324</v>
+        <v>-0.9356</v>
       </c>
       <c r="V14" t="n">
-        <v>2.571</v>
+        <v>2.5659</v>
       </c>
       <c r="W14" t="n">
-        <v>2.8924</v>
+        <v>2.8814</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.8297</v>
+        <v>3.8497</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0722</v>
+        <v>1.0171</v>
       </c>
       <c r="F15" t="n">
-        <v>2.7575</v>
+        <v>2.8326</v>
       </c>
       <c r="G15" t="n">
-        <v>2.2176</v>
+        <v>2.2041</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4042</v>
+        <v>2.3903</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1866</v>
+        <v>-0.1862</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.6506</v>
       </c>
       <c r="K15" t="n">
-        <v>1.745</v>
+        <v>1.7162</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.053</v>
+        <v>-1.0656</v>
       </c>
       <c r="M15" t="n">
-        <v>1.5256</v>
+        <v>1.5536</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6592</v>
+        <v>0.6741</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8663999999999999</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R15" t="n">
-        <v>3.4025</v>
+        <v>3.4145</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5901</v>
+        <v>-0.5609</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6049</v>
+        <v>-0.6044</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0148</v>
+        <v>0.0435</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W15" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="16">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.0588</v>
+        <v>3.5757</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6849</v>
+        <v>1.3672</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3739</v>
+        <v>2.2085</v>
       </c>
       <c r="G16" t="n">
-        <v>3.9468</v>
+        <v>3.9516</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1831</v>
+        <v>0.1919</v>
       </c>
       <c r="I16" t="n">
-        <v>3.7637</v>
+        <v>3.7596</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3621</v>
+        <v>3.3484</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6407</v>
+        <v>0.6378</v>
       </c>
       <c r="L16" t="n">
-        <v>2.7214</v>
+        <v>2.7106</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5847</v>
+        <v>0.6032</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4576</v>
+        <v>-0.4458</v>
       </c>
       <c r="O16" t="n">
-        <v>1.0423</v>
+        <v>1.049</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2775</v>
+        <v>-0.7597</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2521</v>
+        <v>-0.544</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0254</v>
+        <v>-0.2157</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.3535</v>
+        <v>2.6029</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3972</v>
+        <v>1.7124</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9563</v>
+        <v>0.8905</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7952</v>
+        <v>0.7887</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.199</v>
+        <v>-0.2064</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9942</v>
+        <v>0.9951</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5996</v>
+        <v>0.5724</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1172</v>
+        <v>0.0959</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4824</v>
+        <v>0.4764</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1956</v>
+        <v>0.2164</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3162</v>
+        <v>-0.3023</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5118</v>
+        <v>0.5187</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3076</v>
+        <v>-0.0476</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1875</v>
+        <v>0.1691</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1201</v>
+        <v>-0.2168</v>
       </c>
       <c r="V17" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W17" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="18">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5949</v>
+        <v>1.0553</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9036999999999999</v>
+        <v>-0.7076</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4986</v>
+        <v>1.7629</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4419</v>
+        <v>0.4506</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2581</v>
+        <v>0.2721</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1839</v>
+        <v>0.1785</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9494</v>
+        <v>0.9193</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5124</v>
+        <v>0.5031</v>
       </c>
       <c r="L18" t="n">
-        <v>0.437</v>
+        <v>0.4162</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5074</v>
+        <v>-0.4687</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2543</v>
+        <v>-0.231</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2531</v>
+        <v>-0.2377</v>
       </c>
       <c r="P18" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R18" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.9831</v>
+        <v>-1.5319</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8135</v>
+        <v>-0.5766</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.1696</v>
+        <v>-0.9552</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="W18" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. DUKE JR</t>
+          <t>K. AKOBUNDU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3517</v>
+        <v>0.4957</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0148</v>
+        <v>-0.2541</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3665</v>
+        <v>0.7498</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2151</v>
+        <v>0.6746</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8298</v>
+        <v>0.0429</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0449</v>
+        <v>0.6317</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0852</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6264999999999999</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7117</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1299</v>
+        <v>0.0713</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2033</v>
+        <v>-0.5604</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3331</v>
+        <v>0.6317</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>2.4952</v>
+        <v>1.3658</v>
       </c>
       <c r="S19" t="n">
-        <v>0.34</v>
+        <v>0.296</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2461</v>
+        <v>0.2808</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9061</v>
+        <v>0.0152</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.7025</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0927</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. AKOBUNDU</t>
+          <t>P. PAULICAP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2074</v>
+        <v>0.3459</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3678</v>
+        <v>0.1357</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5752</v>
+        <v>0.2102</v>
       </c>
       <c r="G20" t="n">
-        <v>0.668</v>
+        <v>0.3331</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0389</v>
+        <v>0.3331</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6291</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6061</v>
+        <v>0.0172</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6061</v>
+        <v>0.0172</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0619</v>
+        <v>0.3159</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5672</v>
+        <v>0.3159</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6291</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2268</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.361</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0197</v>
+        <v>0.0128</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1603</v>
+        <v>0.1184</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1406</v>
+        <v>-0.1057</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.7071</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.7071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. PAULICAP</t>
+          <t>D. DUKE JR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1955</v>
+        <v>-0.3275</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0173</v>
+        <v>-1.223</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1781</v>
+        <v>0.8955</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3319</v>
+        <v>-0.2181</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3319</v>
+        <v>0.8246</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>-1.0426</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0173</v>
+        <v>-0.1054</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0173</v>
+        <v>0.6098</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3145</v>
+        <v>-0.1127</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3145</v>
+        <v>0.2148</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>-0.3275</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.2276</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.5039</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1364</v>
+        <v>-0.3371</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>0.0692</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1364</v>
+        <v>-0.4063</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.085</v>
+        <v>-0.8515</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0318</v>
+        <v>-2.6979</v>
       </c>
       <c r="F22" t="n">
-        <v>1.9468</v>
+        <v>1.8464</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.2487</v>
+        <v>-2.253</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.2278</v>
+        <v>-1.2373</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.0209</v>
+        <v>-1.0157</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.9506</v>
+        <v>-1.9692</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.1642</v>
+        <v>-1.1796</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2981</v>
+        <v>-0.2838</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0636</v>
+        <v>-0.0578</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P22" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1727</v>
+        <v>0.0569</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6956</v>
+        <v>-0.3417</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5229</v>
+        <v>0.3986</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. PEREZ</t>
+          <t>M. STEINBERGS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.0943</v>
+        <v>-1.0912</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4585</v>
+        <v>-1.2481</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6358</v>
+        <v>0.1569</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.3634</v>
+        <v>-1.0623</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0866</v>
+        <v>0.8894</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.2768</v>
+        <v>-1.9517</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.9666</v>
+        <v>-0.4209</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.1803</v>
+        <v>0.0862</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7864</v>
+        <v>-0.5071</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.3967</v>
+        <v>-0.6414</v>
       </c>
       <c r="N23" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.8032</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4904</v>
+        <v>-1.4446</v>
       </c>
       <c r="P23" t="n">
-        <v>0.6805</v>
+        <v>1.5934</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6805</v>
+        <v>1.8211</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1349</v>
+        <v>-1.6223</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5081</v>
+        <v>-0.5995</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3732</v>
+        <v>-1.0228</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. STEINBERGS</t>
+          <t>D. PEREZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.4645</v>
+        <v>-1.4738</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.4682</v>
+        <v>-0.8205</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0037</v>
+        <v>-0.6533</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.0746</v>
+        <v>-1.3612</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8713</v>
+        <v>-0.0862</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.9459</v>
+        <v>-1.275</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.4067</v>
+        <v>-0.976</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0866</v>
+        <v>-0.1864</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.4932</v>
+        <v>-0.7896</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.668</v>
+        <v>-0.3852</v>
       </c>
       <c r="N24" t="n">
-        <v>0.7847</v>
+        <v>0.1002</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.4526</v>
+        <v>-0.4854</v>
       </c>
       <c r="P24" t="n">
-        <v>1.5878</v>
+        <v>0.6829</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8147</v>
+        <v>0.6829</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.9777</v>
+        <v>-0.2508</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8347</v>
+        <v>0.1555</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.143</v>
+        <v>-0.4063</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-9.501200000000001</v>
+        <v>-8.370100000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-8.9986</v>
+        <v>-8.3385</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.5024999999999999</v>
+        <v>-0.0316</v>
       </c>
       <c r="G25" t="n">
-        <v>-6.2316</v>
+        <v>-6.2437</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.2843</v>
+        <v>-1.2811</v>
       </c>
       <c r="I25" t="n">
-        <v>-4.9473</v>
+        <v>-4.9626</v>
       </c>
       <c r="J25" t="n">
-        <v>-5.5478</v>
+        <v>-5.5879</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.424</v>
+        <v>-1.4381</v>
       </c>
       <c r="L25" t="n">
-        <v>-4.1238</v>
+        <v>-4.1497</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.6839</v>
+        <v>-0.6558</v>
       </c>
       <c r="N25" t="n">
-        <v>0.1397</v>
+        <v>0.157</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.8236</v>
+        <v>-0.8129</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.4283</v>
+        <v>-1.2857</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.1825</v>
+        <v>-0.4743</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.2458</v>
+        <v>-0.8115</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>3.561399999999997</v>
+        <v>5.141299999999998</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.697100000000001</v>
+        <v>-6.010999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>9.258500000000002</v>
+        <v>11.1523</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.2932000000000006</v>
+        <v>-0.2825000000000015</v>
       </c>
       <c r="H26" t="n">
-        <v>4.7183</v>
+        <v>4.7379</v>
       </c>
       <c r="I26" t="n">
-        <v>-5.011399999999999</v>
+        <v>-5.0205</v>
       </c>
       <c r="J26" t="n">
-        <v>0.709500000000002</v>
+        <v>0.4737</v>
       </c>
       <c r="K26" t="n">
-        <v>3.8691</v>
+        <v>3.7407</v>
       </c>
       <c r="L26" t="n">
-        <v>-3.1596</v>
+        <v>-3.266900000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.0028</v>
+        <v>-0.7560999999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>0.8490999999999997</v>
+        <v>0.9973000000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.8517</v>
+        <v>-1.7534</v>
       </c>
       <c r="P26" t="n">
-        <v>10.2074</v>
+        <v>10.2434</v>
       </c>
       <c r="Q26" t="n">
-        <v>-12.4758</v>
+        <v>-12.5198</v>
       </c>
       <c r="R26" t="n">
-        <v>22.6834</v>
+        <v>22.7631</v>
       </c>
       <c r="S26" t="n">
-        <v>-8.6347</v>
+        <v>-7.0849</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.4798</v>
+        <v>-2.4664</v>
       </c>
       <c r="U26" t="n">
-        <v>-6.1549</v>
+        <v>-4.6186</v>
       </c>
       <c r="V26" t="n">
-        <v>2.2818</v>
+        <v>2.265300000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>8.5489</v>
+        <v>8.501399999999999</v>
       </c>
       <c r="X26" t="n">
-        <v>-6.266900000000001</v>
+        <v>-6.2361</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104696_W27.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104696_W27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104696_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0.07140000000000001</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104696_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104696_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104696_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104696_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104696_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104696_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104696_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104696_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104696_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104696_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-8.5015</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104696_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104696_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104696_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104696_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104696_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104696_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104696_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104696_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104696_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104696_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104696_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104696_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-6.2361</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
